--- a/ig/homecareobservation/all-profiles.xlsx
+++ b/ig/homecareobservation/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.1</t>
+    <t>1.2.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-19T07:53:40+00:00</t>
+    <t>2026-06-03T08:12:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
